--- a/content/A1-محتوا.xlsx
+++ b/content/A1-محتوا.xlsx
@@ -497,12 +497,8 @@
           <t>کاربرگ محتوای سطح A1</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="2"/>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -708,7 +704,7 @@
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>موضوع محتوایی</t>
+          <t>ماموریت درس</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
@@ -743,7 +739,7 @@
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>سلام و احوالپرسی، معرفی خود</t>
+          <t>سلام کن و خودت را معرفی کن</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -776,7 +772,7 @@
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>اشیای اطراف ما</t>
+          <t>اسم چیزهای دوروبرت را بگو</t>
         </is>
       </c>
       <c r="E3" s="7" t="n">
@@ -809,7 +805,7 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>پرسیدن درباره افراد</t>
+          <t>بپرس «این کیه؟ این چیه؟»</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
@@ -842,7 +838,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>خانواده</t>
+          <t>خانواده‌ات را معرفی کن</t>
         </is>
       </c>
       <c r="E5" s="7" t="n">
@@ -875,7 +871,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>اعداد، سن، تولد</t>
+          <t>سن و تولد را بگو</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
@@ -908,7 +904,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>کشورها و ملیت‌ها</t>
+          <t>بگو اهل کجایی</t>
         </is>
       </c>
       <c r="E7" s="7" t="n">
@@ -941,7 +937,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>شغل و محل کار</t>
+          <t>درباره شغل و محل کار حرف بزن</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
@@ -974,7 +970,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>کارهای روزمره</t>
+          <t>از کارهای روزمره‌ات بگو</t>
         </is>
       </c>
       <c r="E9" s="7" t="n">
@@ -1007,7 +1003,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>روتین روزانه</t>
+          <t>روتین دیگران را تعریف کن</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
@@ -1040,7 +1036,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>ساعت و روزهای هفته</t>
+          <t>ساعت و روزها را درست بگو</t>
         </is>
       </c>
       <c r="E11" s="7" t="n">
@@ -1073,7 +1069,7 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>علاقه‌مندی‌ها</t>
+          <t>از علاقه‌مندی‌هایت حرف بزن</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
@@ -1106,7 +1102,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>غذا و نوشیدنی</t>
+          <t>درباره غذا و نوشیدنی حرف بزن</t>
         </is>
       </c>
       <c r="E13" s="7" t="n">
@@ -1139,7 +1135,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>در رستوران</t>
+          <t>مثل یک مسافر سفارش بده</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
@@ -1172,7 +1168,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>خانه و اتاق‌ها</t>
+          <t>خانه و اتاقت را توصیف کن</t>
         </is>
       </c>
       <c r="E15" s="7" t="n">
@@ -1205,7 +1201,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>وسایل خانه</t>
+          <t>بگو هر چیز کجاست</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
@@ -1238,7 +1234,7 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>لباس و رنگ‌ها</t>
+          <t>لباس و رنگ‌ها را توصیف کن</t>
         </is>
       </c>
       <c r="E17" s="7" t="n">
@@ -1271,7 +1267,7 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>خرید</t>
+          <t>خرید کن و قیمت بپرس</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
@@ -1304,7 +1300,7 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>آب‌وهوا و فصل‌ها</t>
+          <t>درباره هوا و فصل‌ها حرف بزن</t>
         </is>
       </c>
       <c r="E19" s="7" t="n">
@@ -1337,7 +1333,7 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>توانایی‌ها</t>
+          <t>بگو چه کارهایی بلدی</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
@@ -1370,7 +1366,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>بدن و سلامتی</t>
+          <t>حال جسمت را توضیح بده</t>
         </is>
       </c>
       <c r="E21" s="7" t="n">
@@ -1403,7 +1399,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>حمل‌ونقل و مسیریابی</t>
+          <t>مسیر بپرس و راهنمایی کن</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
@@ -1436,7 +1432,7 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>کارهای در حال انجام</t>
+          <t>بگو همین حالا چه خبر است</t>
         </is>
       </c>
       <c r="E23" s="7" t="n">
@@ -1469,7 +1465,7 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>مقایسه دو زمان</t>
+          <t>فرق عادت و «همین الان» را بفهم</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
@@ -1502,7 +1498,7 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>دیروز کجا بودی</t>
+          <t>بگو دیروز کجا بودی</t>
         </is>
       </c>
       <c r="E25" s="7" t="n">
@@ -1535,7 +1531,7 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>دیروز چه کردی</t>
+          <t>از دیروزت تعریف کن</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
@@ -1568,7 +1564,7 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>سفر گذشته</t>
+          <t>یک سفر گذشته را تعریف کن</t>
         </is>
       </c>
       <c r="E27" s="7" t="n">
@@ -1601,7 +1597,7 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>تعطیلات و سفر</t>
+          <t>از سفر و تعطیلات سؤال بپرس</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
@@ -1634,7 +1630,7 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>برنامه‌های آینده</t>
+          <t>از برنامه‌های آینده‌ات بگو</t>
         </is>
       </c>
       <c r="E29" s="7" t="n">
@@ -1667,7 +1663,7 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>مقایسه کردن</t>
+          <t>دو چیز را با هم مقایسه کن</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
@@ -1700,7 +1696,7 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>مرور سطح A1</t>
+          <t>بهترین‌ها را بگو و A1 را جمع کن</t>
         </is>
       </c>
       <c r="E31" s="7" t="n">

--- a/content/A1-محتوا.xlsx
+++ b/content/A1-محتوا.xlsx
@@ -497,8 +497,12 @@
           <t>کاربرگ محتوای سطح A1</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+    </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -43579,7 +43583,7 @@
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>Ali and I are friends. → ___ are friends.</t>
+          <t>Reza and I are students. → ___ are students.</t>
         </is>
       </c>
       <c r="G3" s="7" t="inlineStr">

--- a/content/A1-محتوا.xlsx
+++ b/content/A1-محتوا.xlsx
@@ -37818,7 +37818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G169"/>
+  <dimension ref="A1:G182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -38661,7 +38661,7 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B26" s="5" t="n">
         <v>1</v>
@@ -38673,12 +38673,12 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Where are you from?</t>
+          <t>How old are you, Ali?</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>اهل کجایی؟</t>
+          <t>علی، چند سالته؟</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -38694,7 +38694,7 @@
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B27" s="7" t="n">
         <v>2</v>
@@ -38706,12 +38706,12 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>I am from Iran. And you?</t>
+          <t>I'm twenty. And you?</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>من اهل ایرانم. تو چطور؟</t>
+          <t>من بیست سالمه. تو چطور؟</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -38727,7 +38727,7 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B28" s="5" t="n">
         <v>3</v>
@@ -38739,12 +38739,12 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>I am from a small city near Shiraz.</t>
+          <t>I'm nineteen. When is your birthday?</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>من اهل شهر کوچکی نزدیک شیرازم.</t>
+          <t>من نوزده سالمه. تولدت کِی است؟</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -38760,7 +38760,7 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B29" s="7" t="n">
         <v>4</v>
@@ -38772,12 +38772,12 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>Is it beautiful?</t>
+          <t>It's in May. We have a party every year.</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>زیباست؟</t>
+          <t>در ماه مه است. هر سال یک مهمانی داریم.</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -38793,7 +38793,7 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B30" s="5" t="n">
         <v>5</v>
@@ -38805,12 +38805,12 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Yes, very beautiful. Where do you live now?</t>
+          <t>Nice! How many people come?</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>بله، خیلی زیبا. الان کجا زندگی می‌کنی؟</t>
+          <t>چه خوب! چند نفر می‌آیند؟</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -38826,7 +38826,7 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B31" s="7" t="n">
         <v>6</v>
@@ -38838,12 +38838,12 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>I live in Tehran. It is a big city.</t>
+          <t>About twenty. My sister brings a big gift.</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>در تهران زندگی می‌کنم. شهر بزرگی است.</t>
+          <t>حدود بیست نفر. خواهرم یک هدیه بزرگ می‌آورد.</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -38859,7 +38859,7 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B32" s="5" t="n">
         <v>1</v>
@@ -38871,12 +38871,12 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>What do you do every day?</t>
+          <t>Where are you from?</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>هر روز چه کار می‌کنی؟</t>
+          <t>اهل کجایی؟</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -38892,7 +38892,7 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B33" s="7" t="n">
         <v>2</v>
@@ -38904,12 +38904,12 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>I wake up at six and I study English.</t>
+          <t>I am from Iran. And you?</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>ساعت شش بیدار می‌شوم و انگلیسی می‌خوانم.</t>
+          <t>من اهل ایرانم. تو چطور؟</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -38925,7 +38925,7 @@
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B34" s="5" t="n">
         <v>3</v>
@@ -38937,12 +38937,12 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Do you go to school?</t>
+          <t>I am from a small city near Shiraz.</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>به مدرسه می‌روی؟</t>
+          <t>من اهل شهر کوچکی نزدیک شیرازم.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -38958,7 +38958,7 @@
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B35" s="7" t="n">
         <v>4</v>
@@ -38970,12 +38970,12 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Yes, I go to school at eight.</t>
+          <t>Is it beautiful?</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>بله، ساعت هشت به مدرسه می‌روم.</t>
+          <t>زیباست؟</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -38991,7 +38991,7 @@
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B36" s="5" t="n">
         <v>5</v>
@@ -39003,12 +39003,12 @@
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>And at night?</t>
+          <t>Yes, very beautiful. Where do you live now?</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>و شب‌ها؟</t>
+          <t>بله، خیلی زیبا. الان کجا زندگی می‌کنی؟</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -39024,7 +39024,7 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B37" s="7" t="n">
         <v>6</v>
@@ -39036,12 +39036,12 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>I read a book and sleep at ten.</t>
+          <t>I live in Tehran. It is a big city.</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>کتاب می‌خوانم و ساعت ده می‌خوابم.</t>
+          <t>در تهران زندگی می‌کنم. شهر بزرگی است.</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -39057,7 +39057,7 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B38" s="5" t="n">
         <v>1</v>
@@ -39069,12 +39069,12 @@
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>What does your brother do?</t>
+          <t>What is your job, Ali?</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>برادرت چه کار می‌کند؟</t>
+          <t>علی، شغلت چیست؟</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -39090,7 +39090,7 @@
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B39" s="7" t="n">
         <v>2</v>
@@ -39102,12 +39102,12 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>He works in an office. He always starts at eight.</t>
+          <t>I'm a nurse. I work in a hospital.</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>در یک دفتر کار می‌کند. همیشه ساعت هشت شروع می‌کند.</t>
+          <t>من پرستارم. در یک بیمارستان کار می‌کنم.</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
@@ -39123,7 +39123,7 @@
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B40" s="5" t="n">
         <v>3</v>
@@ -39135,12 +39135,12 @@
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>Does he study too?</t>
+          <t>Is it hard work?</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>درس هم می‌خواند؟</t>
+          <t>کار سختی است؟</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -39156,7 +39156,7 @@
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B41" s="7" t="n">
         <v>4</v>
@@ -39168,12 +39168,12 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Yes, he studies English every evening.</t>
+          <t>Yes, but I like it. And you?</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>بله، هر عصر انگلیسی می‌خواند.</t>
+          <t>بله، اما دوستش دارم. تو چطور؟</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
@@ -39189,7 +39189,7 @@
     </row>
     <row r="42">
       <c r="A42" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B42" s="5" t="n">
         <v>5</v>
@@ -39201,12 +39201,12 @@
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>He is very busy!</t>
+          <t>I'm an engineer. My office is near the school.</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>خیلی مشغول است!</t>
+          <t>من مهندسم. دفترم نزدیک مدرسه است.</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -39222,7 +39222,7 @@
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B43" s="7" t="n">
         <v>6</v>
@@ -39234,12 +39234,12 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Yes, but he never forgets his family.</t>
+          <t>Is your boss busy today?</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>بله، ولی هرگز خانواده‌اش را فراموش نمی‌کند.</t>
+          <t>رئیست امروز شلوغ است؟</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -39255,10 +39255,10 @@
     </row>
     <row r="44">
       <c r="A44" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
@@ -39267,12 +39267,12 @@
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>Excuse me, what time is it?</t>
+          <t>Very busy. But the work is easy for me.</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>ببخشید، ساعت چند است؟</t>
+          <t>خیلی شلوغ. اما کار برای من آسان است.</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -39288,29 +39288,29 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>It's half past two.</t>
+          <t>What do you do every day?</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>دو و نیم است.</t>
+          <t>هر روز چه کار می‌کنی؟</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
@@ -39321,29 +39321,29 @@
     </row>
     <row r="46">
       <c r="A46" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>Thanks. Is the class on Monday?</t>
+          <t>I wake up at six and I study English.</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>ممنون. کلاس دوشنبه است؟</t>
+          <t>ساعت شش بیدار می‌شوم و انگلیسی می‌خوانم.</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -39354,29 +39354,29 @@
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>No, it's on Wednesday at four o'clock.</t>
+          <t>Do you go to school?</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>نه، چهارشنبه ساعت چهار است.</t>
+          <t>به مدرسه می‌روی؟</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
@@ -39387,29 +39387,29 @@
     </row>
     <row r="48">
       <c r="A48" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>Okay. See you tomorrow!</t>
+          <t>Yes, I go to school at eight.</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>باشه. فردا می‌بینمت!</t>
+          <t>بله، ساعت هشت به مدرسه می‌روم.</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
@@ -39420,29 +39420,29 @@
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Goodbye!</t>
+          <t>And at night?</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>خداحافظ!</t>
+          <t>و شب‌ها؟</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
@@ -39453,29 +39453,29 @@
     </row>
     <row r="50">
       <c r="A50" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>What do you do in your free time?</t>
+          <t>I read a book and sleep at ten.</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>در اوقات فراغتت چه می‌کنی؟</t>
+          <t>کتاب می‌خوانم و ساعت ده می‌خوابم.</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
@@ -39486,29 +39486,29 @@
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>I like reading. And you?</t>
+          <t>What does your brother do?</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>مطالعه دوست دارم. تو چطور؟</t>
+          <t>برادرت چه کار می‌کند؟</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
@@ -39519,29 +39519,29 @@
     </row>
     <row r="52">
       <c r="A52" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>I love music. I play the guitar.</t>
+          <t>He works in an office. He always starts at eight.</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>من عاشق موسیقی‌ام. گیتار می‌نوازم.</t>
+          <t>در یک دفتر کار می‌کند. همیشه ساعت هشت شروع می‌کند.</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
@@ -39552,29 +39552,29 @@
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>Really? That's interesting!</t>
+          <t>Does he study too?</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>واقعاً؟ جالب است!</t>
+          <t>درس هم می‌خواند؟</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
@@ -39585,29 +39585,29 @@
     </row>
     <row r="54">
       <c r="A54" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>Do you like sport?</t>
+          <t>Yes, he studies English every evening.</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>ورزش دوست داری؟</t>
+          <t>بله، هر عصر انگلیسی می‌خواند.</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
@@ -39618,29 +39618,29 @@
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Yes, but I hate running.</t>
+          <t>He is very busy!</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>بله، اما از دویدن متنفرم.</t>
+          <t>خیلی مشغول است!</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
@@ -39651,29 +39651,29 @@
     </row>
     <row r="56">
       <c r="A56" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>Is there any bread?</t>
+          <t>Yes, but he never forgets his family.</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>نان هست؟</t>
+          <t>بله، ولی هرگز خانواده‌اش را فراموش نمی‌کند.</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -39684,29 +39684,29 @@
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>Yes, there is some bread on the table.</t>
+          <t>Excuse me, what time is it?</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>بله، کمی نان روی میز هست.</t>
+          <t>ببخشید، ساعت چند است؟</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
@@ -39717,29 +39717,29 @@
     </row>
     <row r="58">
       <c r="A58" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B58" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>And milk? I want some milk.</t>
+          <t>It's half past two.</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>و شیر؟ کمی شیر می‌خواهم.</t>
+          <t>دو و نیم است.</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
@@ -39750,29 +39750,29 @@
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>No, there isn't any milk.</t>
+          <t>Thanks. Is the class on Monday?</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>نه، هیچ شیری نیست.</t>
+          <t>ممنون. کلاس دوشنبه است؟</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
@@ -39783,29 +39783,29 @@
     </row>
     <row r="60">
       <c r="A60" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>Are there any apples?</t>
+          <t>No, it's on Wednesday at four o'clock.</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>سیب هست؟</t>
+          <t>نه، چهارشنبه ساعت چهار است.</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -39816,29 +39816,29 @@
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Yes, there are three apples.</t>
+          <t>Okay. See you tomorrow!</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>بله، سه تا سیب هست.</t>
+          <t>باشه. فردا می‌بینمت!</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
@@ -39849,29 +39849,29 @@
     </row>
     <row r="62">
       <c r="A62" s="5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>Good evening. A table for two, please.</t>
+          <t>Goodbye!</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>عصر بخیر. یک میز دو نفره، لطفاً.</t>
+          <t>خداحافظ!</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -39882,29 +39882,29 @@
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>Of course. Here is the menu.</t>
+          <t>What do you do in your free time?</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>حتماً. این هم منو.</t>
+          <t>در اوقات فراغتت چه می‌کنی؟</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
@@ -39915,29 +39915,29 @@
     </row>
     <row r="64">
       <c r="A64" s="5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>Thank you. I'd like the soup, please.</t>
+          <t>I like reading. And you?</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>ممنون. سوپ می‌خواهم، لطفاً.</t>
+          <t>مطالعه دوست دارم. تو چطور؟</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
@@ -39948,29 +39948,29 @@
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>And to drink?</t>
+          <t>I love music. I play the guitar.</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>و برای نوشیدن؟</t>
+          <t>من عاشق موسیقی‌ام. گیتار می‌نوازم.</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
@@ -39981,29 +39981,29 @@
     </row>
     <row r="66">
       <c r="A66" s="5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>Can I have some water?</t>
+          <t>Really? That's interesting!</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>می‌شود کمی آب بدهید؟</t>
+          <t>واقعاً؟ جالب است!</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
@@ -40014,29 +40014,29 @@
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>Certainly. Your order is ready soon.</t>
+          <t>Do you like sport?</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>حتماً. سفارشتان به‌زودی آماده است.</t>
+          <t>ورزش دوست داری؟</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
@@ -40047,29 +40047,29 @@
     </row>
     <row r="68">
       <c r="A68" s="5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>Is your flat big?</t>
+          <t>Yes, but I hate running.</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>آپارتمانت بزرگ است؟</t>
+          <t>بله، اما از دویدن متنفرم.</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -40080,29 +40080,29 @@
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>There are three rooms and a kitchen.</t>
+          <t>Is there any bread?</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>سه اتاق و یک آشپزخانه دارد.</t>
+          <t>نان هست؟</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
@@ -40113,29 +40113,29 @@
     </row>
     <row r="70">
       <c r="A70" s="5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B70" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>Is there a balcony?</t>
+          <t>Yes, there is some bread on the table.</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>بالکن هم دارد؟</t>
+          <t>بله، کمی نان روی میز هست.</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
@@ -40146,29 +40146,29 @@
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>Yes, there is a small balcony.</t>
+          <t>And milk? I want some milk.</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>بله، یک بالکن کوچک دارد.</t>
+          <t>و شیر؟ کمی شیر می‌خواهم.</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
@@ -40179,29 +40179,29 @@
     </row>
     <row r="72">
       <c r="A72" s="5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B72" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>And a garden?</t>
+          <t>No, there isn't any milk.</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>و باغچه؟</t>
+          <t>نه، هیچ شیری نیست.</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
@@ -40212,29 +40212,29 @@
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B73" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>No, there isn't a garden.</t>
+          <t>Are there any apples?</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>نه، باغچه ندارد.</t>
+          <t>سیب هست؟</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
@@ -40245,29 +40245,29 @@
     </row>
     <row r="74">
       <c r="A74" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>Where is my bag?</t>
+          <t>Yes, there are three apples.</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>کیفم کجاست؟</t>
+          <t>بله، سه تا سیب هست.</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
@@ -40278,29 +40278,29 @@
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B75" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>It's under the table.</t>
+          <t>Good evening. A table for two, please.</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>زیر میز است.</t>
+          <t>عصر بخیر. یک میز دو نفره، لطفاً.</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
@@ -40311,29 +40311,29 @@
     </row>
     <row r="76">
       <c r="A76" s="5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B76" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>And the keys?</t>
+          <t>Of course. Here is the menu.</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>و کلیدها؟</t>
+          <t>حتماً. این هم منو.</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
@@ -40344,29 +40344,29 @@
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B77" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>They are in your bag.</t>
+          <t>Thank you. I'd like the soup, please.</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>داخل کیفت هستند.</t>
+          <t>ممنون. سوپ می‌خواهم، لطفاً.</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
@@ -40377,29 +40377,29 @@
     </row>
     <row r="78">
       <c r="A78" s="5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B78" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>Where is the lamp?</t>
+          <t>And to drink?</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>چراغ کجاست؟</t>
+          <t>و برای نوشیدن؟</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -40410,29 +40410,29 @@
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B79" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>It's next to the bed.</t>
+          <t>Can I have some water?</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>کنار تخت است.</t>
+          <t>می‌شود کمی آب بدهید؟</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
@@ -40443,29 +40443,29 @@
     </row>
     <row r="80">
       <c r="A80" s="5" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B80" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>I have got a new coat.</t>
+          <t>Certainly. Your order is ready soon.</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>یک پالتوی نو دارم.</t>
+          <t>حتماً. سفارشتان به‌زودی آماده است.</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -40476,29 +40476,29 @@
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B81" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>What colour is it?</t>
+          <t>Is your flat big?</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>چه رنگی است؟</t>
+          <t>آپارتمانت بزرگ است؟</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
@@ -40509,29 +40509,29 @@
     </row>
     <row r="82">
       <c r="A82" s="5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B82" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>It's red. Do you like it?</t>
+          <t>There are three rooms and a kitchen.</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>قرمز است. دوستش داری؟</t>
+          <t>سه اتاق و یک آشپزخانه دارد.</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -40542,29 +40542,29 @@
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B83" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Yes! I have got a green one.</t>
+          <t>Is there a balcony?</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>بله! من یک سبز دارم.</t>
+          <t>بالکن هم دارد؟</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr">
@@ -40575,29 +40575,29 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B84" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>Have you got a scarf too?</t>
+          <t>Yes, there is a small balcony.</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>شال گردن هم داری؟</t>
+          <t>بله، یک بالکن کوچک دارد.</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
@@ -40608,29 +40608,29 @@
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B85" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>No, I haven't.</t>
+          <t>And a garden?</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>نه، ندارم.</t>
+          <t>و باغچه؟</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
@@ -40641,29 +40641,29 @@
     </row>
     <row r="86">
       <c r="A86" s="5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B86" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>Excuse me, how much is this shirt?</t>
+          <t>No, there isn't a garden.</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>ببخشید، این پیراهن چند است؟</t>
+          <t>نه، باغچه ندارد.</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
@@ -40674,29 +40674,29 @@
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B87" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>It's cheap. Only two hundred.</t>
+          <t>Where is my bag?</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>ارزان است. فقط دویست.</t>
+          <t>کیفم کجاست؟</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
@@ -40707,29 +40707,29 @@
     </row>
     <row r="88">
       <c r="A88" s="5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B88" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>And how much are these shoes?</t>
+          <t>It's under the table.</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>و این کفش‌ها چند هستند؟</t>
+          <t>زیر میز است.</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
@@ -40740,29 +40740,29 @@
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B89" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>Those are expensive, I'm afraid.</t>
+          <t>And the keys?</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>متأسفانه آن‌ها گران هستند.</t>
+          <t>و کلیدها؟</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
@@ -40773,29 +40773,29 @@
     </row>
     <row r="90">
       <c r="A90" s="5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B90" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>Can I try the shirt on?</t>
+          <t>They are in your bag.</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>می‌توانم پیراهن را پرو کنم؟</t>
+          <t>داخل کیفت هستند.</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
@@ -40806,29 +40806,29 @@
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B91" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>Of course. Here you are.</t>
+          <t>Where is the lamp?</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>حتماً. بفرمایید.</t>
+          <t>چراغ کجاست؟</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
@@ -40839,29 +40839,29 @@
     </row>
     <row r="92">
       <c r="A92" s="5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B92" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>How is the weather today?</t>
+          <t>It's next to the bed.</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>امروز هوا چطور است؟</t>
+          <t>کنار تخت است.</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
@@ -40872,29 +40872,29 @@
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B93" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>It's cold and cloudy.</t>
+          <t>I have got a new coat.</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>سرد و ابری است.</t>
+          <t>یک پالتوی نو دارم.</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G93" s="7" t="inlineStr">
@@ -40905,29 +40905,29 @@
     </row>
     <row r="94">
       <c r="A94" s="5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B94" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>Is it raining?</t>
+          <t>What colour is it?</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>باران می‌بارد؟</t>
+          <t>چه رنگی است؟</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
@@ -40938,29 +40938,29 @@
     </row>
     <row r="95">
       <c r="A95" s="7" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B95" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Not now, but take an umbrella.</t>
+          <t>It's red. Do you like it?</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>الان نه، اما چتر بردار.</t>
+          <t>قرمز است. دوستش داری؟</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G95" s="7" t="inlineStr">
@@ -40971,29 +40971,29 @@
     </row>
     <row r="96">
       <c r="A96" s="5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B96" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>What about tomorrow?</t>
+          <t>Yes! I have got a green one.</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>فردا چطور؟</t>
+          <t>بله! من یک سبز دارم.</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
@@ -41004,29 +41004,29 @@
     </row>
     <row r="97">
       <c r="A97" s="7" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B97" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>It's sunny and warm tomorrow.</t>
+          <t>Have you got a scarf too?</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>فردا آفتابی و مطبوع است.</t>
+          <t>شال گردن هم داری؟</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr">
@@ -41037,29 +41037,29 @@
     </row>
     <row r="98">
       <c r="A98" s="5" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B98" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>Can you swim?</t>
+          <t>No, I haven't.</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>می‌توانی شنا کنی؟</t>
+          <t>نه، ندارم.</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
@@ -41070,29 +41070,29 @@
     </row>
     <row r="99">
       <c r="A99" s="7" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B99" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>Yes, I can swim well.</t>
+          <t>Excuse me, how much is this shirt?</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>بله، خوب شنا می‌کنم.</t>
+          <t>ببخشید، این پیراهن چند است؟</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
@@ -41103,29 +41103,29 @@
     </row>
     <row r="100">
       <c r="A100" s="5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B100" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>Can you drive?</t>
+          <t>It's cheap. Only two hundred.</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>رانندگی بلدی؟</t>
+          <t>ارزان است. فقط دویست.</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -41136,29 +41136,29 @@
     </row>
     <row r="101">
       <c r="A101" s="7" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B101" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>No, I can't drive.</t>
+          <t>And how much are these shoes?</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>نه، رانندگی بلد نیستم.</t>
+          <t>و این کفش‌ها چند هستند؟</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
@@ -41169,29 +41169,29 @@
     </row>
     <row r="102">
       <c r="A102" s="5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B102" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>Can you help me tomorrow?</t>
+          <t>Those are expensive, I'm afraid.</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>فردا می‌توانی کمکم کنی؟</t>
+          <t>متأسفانه آن‌ها گران هستند.</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
@@ -41202,29 +41202,29 @@
     </row>
     <row r="103">
       <c r="A103" s="7" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B103" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>Yes, of course I can.</t>
+          <t>Can I try the shirt on?</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>بله، البته که می‌توانم.</t>
+          <t>می‌توانم پیراهن را پرو کنم؟</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G103" s="7" t="inlineStr">
@@ -41235,29 +41235,29 @@
     </row>
     <row r="104">
       <c r="A104" s="5" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B104" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>How are you today?</t>
+          <t>Of course. Here you are.</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>امروز حالت چطور است؟</t>
+          <t>حتماً. بفرمایید.</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
@@ -41268,29 +41268,29 @@
     </row>
     <row r="105">
       <c r="A105" s="7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B105" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>Not good. I have a headache.</t>
+          <t>How is the weather today?</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>خوب نیستم. سردرد دارم.</t>
+          <t>امروز هوا چطور است؟</t>
         </is>
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G105" s="7" t="inlineStr">
@@ -41301,29 +41301,29 @@
     </row>
     <row r="106">
       <c r="A106" s="5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B106" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>Have you got a fever?</t>
+          <t>It's cold and cloudy.</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>تب هم داری؟</t>
+          <t>سرد و ابری است.</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
@@ -41334,29 +41334,29 @@
     </row>
     <row r="107">
       <c r="A107" s="7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B107" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>A little. I feel very tired.</t>
+          <t>Is it raining?</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>کمی. خیلی خسته‌ام.</t>
+          <t>باران می‌بارد؟</t>
         </is>
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G107" s="7" t="inlineStr">
@@ -41367,29 +41367,29 @@
     </row>
     <row r="108">
       <c r="A108" s="5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B108" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>You should rest at home.</t>
+          <t>Not now, but take an umbrella.</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>باید در خانه استراحت کنی.</t>
+          <t>الان نه، اما چتر بردار.</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
@@ -41400,29 +41400,29 @@
     </row>
     <row r="109">
       <c r="A109" s="7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B109" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>Yes, and I should take some medicine.</t>
+          <t>What about tomorrow?</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>بله، و باید دارو بخورم.</t>
+          <t>فردا چطور؟</t>
         </is>
       </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G109" s="7" t="inlineStr">
@@ -41433,29 +41433,29 @@
     </row>
     <row r="110">
       <c r="A110" s="5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B110" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>Excuse me, where is the station?</t>
+          <t>It's sunny and warm tomorrow.</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>ببخشید، ایستگاه کجاست؟</t>
+          <t>فردا آفتابی و مطبوع است.</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
@@ -41466,29 +41466,29 @@
     </row>
     <row r="111">
       <c r="A111" s="7" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B111" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>Go straight on and turn left.</t>
+          <t>Can you swim?</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>مستقیم برو و بپیچ چپ.</t>
+          <t>می‌توانی شنا کنی؟</t>
         </is>
       </c>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G111" s="7" t="inlineStr">
@@ -41499,29 +41499,29 @@
     </row>
     <row r="112">
       <c r="A112" s="5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B112" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>Is it far from here?</t>
+          <t>Yes, I can swim well.</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>از اینجا دور است؟</t>
+          <t>بله، خوب شنا می‌کنم.</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
@@ -41532,29 +41532,29 @@
     </row>
     <row r="113">
       <c r="A113" s="7" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B113" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>No, it's very near. Five minutes.</t>
+          <t>Can you drive?</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>نه، خیلی نزدیک است. پنج دقیقه.</t>
+          <t>رانندگی بلدی؟</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">
@@ -41565,29 +41565,29 @@
     </row>
     <row r="114">
       <c r="A114" s="5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B114" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>Thank you very much!</t>
+          <t>No, I can't drive.</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>خیلی ممنون!</t>
+          <t>نه، رانندگی بلد نیستم.</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
@@ -41598,29 +41598,29 @@
     </row>
     <row r="115">
       <c r="A115" s="7" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B115" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>You're welcome. Cross the bridge first.</t>
+          <t>Can you help me tomorrow?</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>خواهش می‌کنم. اول از پل رد شو.</t>
+          <t>فردا می‌توانی کمکم کنی؟</t>
         </is>
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G115" s="7" t="inlineStr">
@@ -41631,29 +41631,29 @@
     </row>
     <row r="116">
       <c r="A116" s="5" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B116" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>What are you doing?</t>
+          <t>Yes, of course I can.</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>داری چه کار می‌کنی؟</t>
+          <t>بله، البته که می‌توانم.</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
@@ -41664,29 +41664,29 @@
     </row>
     <row r="117">
       <c r="A117" s="7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B117" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>I'm working. And you?</t>
+          <t>How are you today?</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>دارم کار می‌کنم. تو چطور؟</t>
+          <t>امروز حالت چطور است؟</t>
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G117" s="7" t="inlineStr">
@@ -41697,29 +41697,29 @@
     </row>
     <row r="118">
       <c r="A118" s="5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B118" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>I'm watching a film.</t>
+          <t>Not good. I have a headache.</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>دارم فیلم می‌بینم.</t>
+          <t>خوب نیستم. سردرد دارم.</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
@@ -41730,29 +41730,29 @@
     </row>
     <row r="119">
       <c r="A119" s="7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B119" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
-          <t>Is Sara sleeping?</t>
+          <t>Have you got a fever?</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>سارا خوابیده؟</t>
+          <t>تب هم داری؟</t>
         </is>
       </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G119" s="7" t="inlineStr">
@@ -41763,29 +41763,29 @@
     </row>
     <row r="120">
       <c r="A120" s="5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B120" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>No, she isn't. She's studying.</t>
+          <t>A little. I feel very tired.</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
         <is>
-          <t>نه، دارد درس می‌خواند.</t>
+          <t>کمی. خیلی خسته‌ام.</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
@@ -41796,29 +41796,29 @@
     </row>
     <row r="121">
       <c r="A121" s="7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B121" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>She's always busy!</t>
+          <t>You should rest at home.</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>همیشه مشغول است!</t>
+          <t>باید در خانه استراحت کنی.</t>
         </is>
       </c>
       <c r="F121" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G121" s="7" t="inlineStr">
@@ -41829,29 +41829,29 @@
     </row>
     <row r="122">
       <c r="A122" s="5" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B122" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>How do you go to work?</t>
+          <t>Yes, and I should take some medicine.</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>چطور سر کار می‌روی؟</t>
+          <t>بله، و باید دارو بخورم.</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
@@ -41862,29 +41862,29 @@
     </row>
     <row r="123">
       <c r="A123" s="7" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B123" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>I usually walk, but today I'm taking the bus.</t>
+          <t>Excuse me, where is the station?</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>معمولاً پیاده می‌روم، اما امروز اتوبوس سوار می‌شوم.</t>
+          <t>ببخشید، ایستگاه کجاست؟</t>
         </is>
       </c>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G123" s="7" t="inlineStr">
@@ -41895,29 +41895,29 @@
     </row>
     <row r="124">
       <c r="A124" s="5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B124" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>Why?</t>
+          <t>Go straight on and turn left.</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>چرا؟</t>
+          <t>مستقیم برو و بپیچ چپ.</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
@@ -41928,29 +41928,29 @@
     </row>
     <row r="125">
       <c r="A125" s="7" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B125" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>Because it's raining now.</t>
+          <t>Is it far from here?</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>چون الان باران می‌بارد.</t>
+          <t>از اینجا دور است؟</t>
         </is>
       </c>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G125" s="7" t="inlineStr">
@@ -41961,29 +41961,29 @@
     </row>
     <row r="126">
       <c r="A126" s="5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B126" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>Do you always start at eight?</t>
+          <t>No, it's very near. Five minutes.</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>همیشه ساعت هشت شروع می‌کنی؟</t>
+          <t>نه، خیلی نزدیک است. پنج دقیقه.</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
@@ -41994,29 +41994,29 @@
     </row>
     <row r="127">
       <c r="A127" s="7" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B127" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>Yes, and I never finish before five.</t>
+          <t>Thank you very much!</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>بله، و هرگز قبل از پنج تمام نمی‌کنم.</t>
+          <t>خیلی ممنون!</t>
         </is>
       </c>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G127" s="7" t="inlineStr">
@@ -42027,29 +42027,29 @@
     </row>
     <row r="128">
       <c r="A128" s="5" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B128" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>Where were you yesterday?</t>
+          <t>You're welcome. Cross the bridge first.</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
-          <t>دیروز کجا بودی؟</t>
+          <t>خواهش می‌کنم. اول از پل رد شو.</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
@@ -42060,29 +42060,29 @@
     </row>
     <row r="129">
       <c r="A129" s="7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B129" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>I was at home. I was very tired.</t>
+          <t>What are you doing?</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>خانه بودم. خیلی خسته بودم.</t>
+          <t>داری چه کار می‌کنی؟</t>
         </is>
       </c>
       <c r="F129" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G129" s="7" t="inlineStr">
@@ -42093,29 +42093,29 @@
     </row>
     <row r="130">
       <c r="A130" s="5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B130" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>Were you ill?</t>
+          <t>I'm working. And you?</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
         <is>
-          <t>مریض بودی؟</t>
+          <t>دارم کار می‌کنم. تو چطور؟</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
@@ -42126,29 +42126,29 @@
     </row>
     <row r="131">
       <c r="A131" s="7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B131" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>No, I wasn't. Just tired.</t>
+          <t>I'm watching a film.</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>نه، فقط خسته.</t>
+          <t>دارم فیلم می‌بینم.</t>
         </is>
       </c>
       <c r="F131" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G131" s="7" t="inlineStr">
@@ -42159,29 +42159,29 @@
     </row>
     <row r="132">
       <c r="A132" s="5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B132" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>We were at the park. It was beautiful.</t>
+          <t>Is Sara sleeping?</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>ما پارک بودیم. زیبا بود.</t>
+          <t>سارا خوابیده؟</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
@@ -42192,29 +42192,29 @@
     </row>
     <row r="133">
       <c r="A133" s="7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B133" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>Was the weather good?</t>
+          <t>No, she isn't. She's studying.</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>هوا خوب بود؟</t>
+          <t>نه، دارد درس می‌خواند.</t>
         </is>
       </c>
       <c r="F133" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G133" s="7" t="inlineStr">
@@ -42225,29 +42225,29 @@
     </row>
     <row r="134">
       <c r="A134" s="5" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B134" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>What did you do at the weekend?</t>
+          <t>She's always busy!</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t>آخر هفته چه کار کردی؟</t>
+          <t>همیشه مشغول است!</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
@@ -42258,29 +42258,29 @@
     </row>
     <row r="135">
       <c r="A135" s="7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B135" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D135" s="8" t="inlineStr">
         <is>
-          <t>We played football and watched a film.</t>
+          <t>How do you go to work?</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>فوتبال بازی کردیم و فیلم دیدیم.</t>
+          <t>چطور سر کار می‌روی؟</t>
         </is>
       </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G135" s="7" t="inlineStr">
@@ -42291,29 +42291,29 @@
     </row>
     <row r="136">
       <c r="A136" s="5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B136" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
         <is>
-          <t>Did you enjoy it?</t>
+          <t>I usually walk, but today I'm taking the bus.</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
         <is>
-          <t>لذت بردی؟</t>
+          <t>معمولاً پیاده می‌روم، اما امروز اتوبوس سوار می‌شوم.</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
@@ -42324,29 +42324,29 @@
     </row>
     <row r="137">
       <c r="A137" s="7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B137" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C137" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D137" s="8" t="inlineStr">
         <is>
-          <t>Yes! And I called my friend.</t>
+          <t>Why?</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>بله! و به دوستم زنگ زدم.</t>
+          <t>چرا؟</t>
         </is>
       </c>
       <c r="F137" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G137" s="7" t="inlineStr">
@@ -42357,29 +42357,29 @@
     </row>
     <row r="138">
       <c r="A138" s="5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B138" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>I stayed at home and studied.</t>
+          <t>Because it's raining now.</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
         <is>
-          <t>من خانه ماندم و درس خواندم.</t>
+          <t>چون الان باران می‌بارد.</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
@@ -42390,29 +42390,29 @@
     </row>
     <row r="139">
       <c r="A139" s="7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B139" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C139" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D139" s="8" t="inlineStr">
         <is>
-          <t>You worked very hard.</t>
+          <t>Do you always start at eight?</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>خیلی سخت کار کردی.</t>
+          <t>همیشه ساعت هشت شروع می‌کنی؟</t>
         </is>
       </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G139" s="7" t="inlineStr">
@@ -42423,29 +42423,29 @@
     </row>
     <row r="140">
       <c r="A140" s="5" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B140" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>Where did you go last summer?</t>
+          <t>Yes, and I never finish before five.</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
         <is>
-          <t>تابستان گذشته کجا رفتی؟</t>
+          <t>بله، و هرگز قبل از پنج تمام نمی‌کنم.</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
@@ -42456,29 +42456,29 @@
     </row>
     <row r="141">
       <c r="A141" s="7" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B141" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D141" s="8" t="inlineStr">
         <is>
-          <t>I went to Tehran with my family.</t>
+          <t>Where were you yesterday?</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>با خانواده‌ام به تهران رفتم.</t>
+          <t>دیروز کجا بودی؟</t>
         </is>
       </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G141" s="7" t="inlineStr">
@@ -42489,29 +42489,29 @@
     </row>
     <row r="142">
       <c r="A142" s="5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B142" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
         <is>
-          <t>What did you see there?</t>
+          <t>I was at home. I was very tired.</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
         <is>
-          <t>آنجا چه دیدی؟</t>
+          <t>خانه بودم. خیلی خسته بودم.</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
@@ -42522,29 +42522,29 @@
     </row>
     <row r="143">
       <c r="A143" s="7" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B143" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C143" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D143" s="8" t="inlineStr">
         <is>
-          <t>We saw the city and ate good food.</t>
+          <t>Were you ill?</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>شهر را دیدیم و غذای خوب خوردیم.</t>
+          <t>مریض بودی؟</t>
         </is>
       </c>
       <c r="F143" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G143" s="7" t="inlineStr">
@@ -42555,29 +42555,29 @@
     </row>
     <row r="144">
       <c r="A144" s="5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B144" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr">
         <is>
-          <t>Did you take photos?</t>
+          <t>No, I wasn't. Just tired.</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
         <is>
-          <t>عکس گرفتی؟</t>
+          <t>نه، فقط خسته.</t>
         </is>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
@@ -42588,29 +42588,29 @@
     </row>
     <row r="145">
       <c r="A145" s="7" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B145" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C145" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D145" s="8" t="inlineStr">
         <is>
-          <t>Yes, I took many photos.</t>
+          <t>We were at the park. It was beautiful.</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>بله، عکس‌های زیادی گرفتم.</t>
+          <t>ما پارک بودیم. زیبا بود.</t>
         </is>
       </c>
       <c r="F145" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G145" s="7" t="inlineStr">
@@ -42621,29 +42621,29 @@
     </row>
     <row r="146">
       <c r="A146" s="5" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B146" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D146" s="6" t="inlineStr">
         <is>
-          <t>Did you like the holiday?</t>
+          <t>Was the weather good?</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
         <is>
-          <t>تعطیلات را دوست داشتی؟</t>
+          <t>هوا خوب بود؟</t>
         </is>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr">
@@ -42654,29 +42654,29 @@
     </row>
     <row r="147">
       <c r="A147" s="7" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B147" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C147" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D147" s="8" t="inlineStr">
         <is>
-          <t>Yes, I did. It was perfect.</t>
+          <t>What did you do at the weekend?</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>بله. عالی بود.</t>
+          <t>آخر هفته چه کار کردی؟</t>
         </is>
       </c>
       <c r="F147" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G147" s="7" t="inlineStr">
@@ -42687,29 +42687,29 @@
     </row>
     <row r="148">
       <c r="A148" s="5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B148" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr">
         <is>
-          <t>Where did you stay?</t>
+          <t>We played football and watched a film.</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr">
         <is>
-          <t>کجا ماندی؟</t>
+          <t>فوتبال بازی کردیم و فیلم دیدیم.</t>
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
@@ -42720,29 +42720,29 @@
     </row>
     <row r="149">
       <c r="A149" s="7" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B149" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C149" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D149" s="8" t="inlineStr">
         <is>
-          <t>In a small hotel near the beach.</t>
+          <t>Did you enjoy it?</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>در هتل کوچکی نزدیک ساحل.</t>
+          <t>لذت بردی؟</t>
         </is>
       </c>
       <c r="F149" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G149" s="7" t="inlineStr">
@@ -42753,29 +42753,29 @@
     </row>
     <row r="150">
       <c r="A150" s="5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B150" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr">
         <is>
-          <t>Was it expensive?</t>
+          <t>Yes! And I called my friend.</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr">
         <is>
-          <t>گران بود؟</t>
+          <t>بله! و به دوستم زنگ زدم.</t>
         </is>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G150" s="5" t="inlineStr">
@@ -42786,29 +42786,29 @@
     </row>
     <row r="151">
       <c r="A151" s="7" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B151" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C151" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D151" s="8" t="inlineStr">
         <is>
-          <t>No, it wasn't. It was cheap and clean.</t>
+          <t>I stayed at home and studied.</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>نه. ارزان و تمیز بود.</t>
+          <t>من خانه ماندم و درس خواندم.</t>
         </is>
       </c>
       <c r="F151" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G151" s="7" t="inlineStr">
@@ -42819,29 +42819,29 @@
     </row>
     <row r="152">
       <c r="A152" s="5" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B152" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D152" s="6" t="inlineStr">
         <is>
-          <t>What are you going to do next week?</t>
+          <t>You worked very hard.</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr">
         <is>
-          <t>هفته آینده قرار است چه کار کنی؟</t>
+          <t>خیلی سخت کار کردی.</t>
         </is>
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr">
@@ -42852,29 +42852,29 @@
     </row>
     <row r="153">
       <c r="A153" s="7" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B153" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C153" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D153" s="8" t="inlineStr">
         <is>
-          <t>I'm going to start an English course.</t>
+          <t>Where did you go last summer?</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>قرار است یک دوره انگلیسی شروع کنم.</t>
+          <t>تابستان گذشته کجا رفتی؟</t>
         </is>
       </c>
       <c r="F153" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G153" s="7" t="inlineStr">
@@ -42885,29 +42885,29 @@
     </row>
     <row r="154">
       <c r="A154" s="5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B154" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D154" s="6" t="inlineStr">
         <is>
-          <t>That's great! Where?</t>
+          <t>I went to Tehran with my family.</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr">
         <is>
-          <t>عالی است! کجا؟</t>
+          <t>با خانواده‌ام به تهران رفتم.</t>
         </is>
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr">
@@ -42918,29 +42918,29 @@
     </row>
     <row r="155">
       <c r="A155" s="7" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B155" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C155" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D155" s="8" t="inlineStr">
         <is>
-          <t>At the university near my house.</t>
+          <t>What did you see there?</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>در دانشگاه نزدیک خانه‌ام.</t>
+          <t>آنجا چه دیدی؟</t>
         </is>
       </c>
       <c r="F155" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G155" s="7" t="inlineStr">
@@ -42951,29 +42951,29 @@
     </row>
     <row r="156">
       <c r="A156" s="5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B156" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D156" s="6" t="inlineStr">
         <is>
-          <t>Are you going to work too?</t>
+          <t>We saw the city and ate good food.</t>
         </is>
       </c>
       <c r="E156" s="6" t="inlineStr">
         <is>
-          <t>قرار است کار هم بکنی؟</t>
+          <t>شهر را دیدیم و غذای خوب خوردیم.</t>
         </is>
       </c>
       <c r="F156" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
@@ -42984,29 +42984,29 @@
     </row>
     <row r="157">
       <c r="A157" s="7" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B157" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C157" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D157" s="8" t="inlineStr">
         <is>
-          <t>Yes, and I'm going to save money.</t>
+          <t>Did you take photos?</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>بله، و قرار است پول پس‌انداز کنم.</t>
+          <t>عکس گرفتی؟</t>
         </is>
       </c>
       <c r="F157" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G157" s="7" t="inlineStr">
@@ -43017,29 +43017,29 @@
     </row>
     <row r="158">
       <c r="A158" s="5" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B158" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D158" s="6" t="inlineStr">
         <is>
-          <t>Which city is bigger, Tehran or Yazd?</t>
+          <t>Yes, I took many photos.</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr">
         <is>
-          <t>کدام شهر بزرگ‌تر است، تهران یا یزد؟</t>
+          <t>بله، عکس‌های زیادی گرفتم.</t>
         </is>
       </c>
       <c r="F158" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G158" s="5" t="inlineStr">
@@ -43050,29 +43050,29 @@
     </row>
     <row r="159">
       <c r="A159" s="7" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B159" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C159" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D159" s="8" t="inlineStr">
         <is>
-          <t>Tehran is much bigger.</t>
+          <t>Did you like the holiday?</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>تهران خیلی بزرگ‌تر است.</t>
+          <t>تعطیلات را دوست داشتی؟</t>
         </is>
       </c>
       <c r="F159" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G159" s="7" t="inlineStr">
@@ -43083,29 +43083,29 @@
     </row>
     <row r="160">
       <c r="A160" s="5" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B160" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr">
         <is>
-          <t>Is your brother older than you?</t>
+          <t>Yes, I did. It was perfect.</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr">
         <is>
-          <t>برادرت از تو مسن‌تر است؟</t>
+          <t>بله. عالی بود.</t>
         </is>
       </c>
       <c r="F160" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr">
@@ -43116,29 +43116,29 @@
     </row>
     <row r="161">
       <c r="A161" s="7" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B161" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C161" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D161" s="8" t="inlineStr">
         <is>
-          <t>Yes, he's two years older.</t>
+          <t>Where did you stay?</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>بله، دو سال مسن‌تر است.</t>
+          <t>کجا ماندی؟</t>
         </is>
       </c>
       <c r="F161" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G161" s="7" t="inlineStr">
@@ -43149,29 +43149,29 @@
     </row>
     <row r="162">
       <c r="A162" s="5" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B162" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr">
         <is>
-          <t>This tea is better than that one.</t>
+          <t>In a small hotel near the beach.</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr">
         <is>
-          <t>این چای از آن یکی بهتر است.</t>
+          <t>در هتل کوچکی نزدیک ساحل.</t>
         </is>
       </c>
       <c r="F162" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G162" s="5" t="inlineStr">
@@ -43182,29 +43182,29 @@
     </row>
     <row r="163">
       <c r="A163" s="7" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B163" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C163" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D163" s="8" t="inlineStr">
         <is>
-          <t>I agree. And it's cheaper too.</t>
+          <t>Was it expensive?</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t>موافقم. و ارزان‌تر هم هست.</t>
+          <t>گران بود؟</t>
         </is>
       </c>
       <c r="F163" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G163" s="7" t="inlineStr">
@@ -43215,29 +43215,29 @@
     </row>
     <row r="164">
       <c r="A164" s="5" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B164" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr">
         <is>
-          <t>How was your week?</t>
+          <t>No, it wasn't. It was cheap and clean.</t>
         </is>
       </c>
       <c r="E164" s="6" t="inlineStr">
         <is>
-          <t>هفته‌ات چطور بود؟</t>
+          <t>نه. ارزان و تمیز بود.</t>
         </is>
       </c>
       <c r="F164" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G164" s="5" t="inlineStr">
@@ -43248,29 +43248,29 @@
     </row>
     <row r="165">
       <c r="A165" s="7" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B165" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C165" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D165" s="8" t="inlineStr">
         <is>
-          <t>It was the best week of the year!</t>
+          <t>What are you going to do next week?</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>بهترین هفته سال بود!</t>
+          <t>هفته آینده قرار است چه کار کنی؟</t>
         </is>
       </c>
       <c r="F165" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G165" s="7" t="inlineStr">
@@ -43281,29 +43281,29 @@
     </row>
     <row r="166">
       <c r="A166" s="5" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B166" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
         <is>
-          <t>Why? What happened?</t>
+          <t>I'm going to start an English course.</t>
         </is>
       </c>
       <c r="E166" s="6" t="inlineStr">
         <is>
-          <t>چرا؟ چه شد؟</t>
+          <t>قرار است یک دوره انگلیسی شروع کنم.</t>
         </is>
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr">
@@ -43314,29 +43314,29 @@
     </row>
     <row r="167">
       <c r="A167" s="7" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B167" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C167" s="7" t="inlineStr">
         <is>
-          <t>نفر دوم</t>
+          <t>نفر اول</t>
         </is>
       </c>
       <c r="D167" s="8" t="inlineStr">
         <is>
-          <t>I finished level A1.</t>
+          <t>That's great! Where?</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
         <is>
-          <t>سطح A1 را تمام کردم.</t>
+          <t>عالی است! کجا؟</t>
         </is>
       </c>
       <c r="F167" s="7" t="inlineStr">
         <is>
-          <t>مرد</t>
+          <t>زن</t>
         </is>
       </c>
       <c r="G167" s="7" t="inlineStr">
@@ -43347,29 +43347,29 @@
     </row>
     <row r="168">
       <c r="A168" s="5" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B168" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>نفر اول</t>
+          <t>نفر دوم</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr">
         <is>
-          <t>Well done! I'm proud of you.</t>
+          <t>At the university near my house.</t>
         </is>
       </c>
       <c r="E168" s="6" t="inlineStr">
         <is>
-          <t>آفرین! به تو افتخار می‌کنم.</t>
+          <t>در دانشگاه نزدیک خانه‌ام.</t>
         </is>
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
-          <t>زن</t>
+          <t>مرد</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr">
@@ -43380,32 +43380,461 @@
     </row>
     <row r="169">
       <c r="A169" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B169" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C169" s="7" t="inlineStr">
+        <is>
+          <t>نفر اول</t>
+        </is>
+      </c>
+      <c r="D169" s="8" t="inlineStr">
+        <is>
+          <t>Are you going to work too?</t>
+        </is>
+      </c>
+      <c r="E169" s="8" t="inlineStr">
+        <is>
+          <t>قرار است کار هم بکنی؟</t>
+        </is>
+      </c>
+      <c r="F169" s="7" t="inlineStr">
+        <is>
+          <t>زن</t>
+        </is>
+      </c>
+      <c r="G169" s="7" t="inlineStr">
+        <is>
+          <t>آماده</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B170" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C170" s="5" t="inlineStr">
+        <is>
+          <t>نفر دوم</t>
+        </is>
+      </c>
+      <c r="D170" s="6" t="inlineStr">
+        <is>
+          <t>Yes, and I'm going to save money.</t>
+        </is>
+      </c>
+      <c r="E170" s="6" t="inlineStr">
+        <is>
+          <t>بله، و قرار است پول پس‌انداز کنم.</t>
+        </is>
+      </c>
+      <c r="F170" s="5" t="inlineStr">
+        <is>
+          <t>مرد</t>
+        </is>
+      </c>
+      <c r="G170" s="5" t="inlineStr">
+        <is>
+          <t>آماده</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B171" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C171" s="7" t="inlineStr">
+        <is>
+          <t>نفر اول</t>
+        </is>
+      </c>
+      <c r="D171" s="8" t="inlineStr">
+        <is>
+          <t>Which city is bigger, Tehran or Yazd?</t>
+        </is>
+      </c>
+      <c r="E171" s="8" t="inlineStr">
+        <is>
+          <t>کدام شهر بزرگ‌تر است، تهران یا یزد؟</t>
+        </is>
+      </c>
+      <c r="F171" s="7" t="inlineStr">
+        <is>
+          <t>زن</t>
+        </is>
+      </c>
+      <c r="G171" s="7" t="inlineStr">
+        <is>
+          <t>آماده</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B172" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C172" s="5" t="inlineStr">
+        <is>
+          <t>نفر دوم</t>
+        </is>
+      </c>
+      <c r="D172" s="6" t="inlineStr">
+        <is>
+          <t>Tehran is much bigger.</t>
+        </is>
+      </c>
+      <c r="E172" s="6" t="inlineStr">
+        <is>
+          <t>تهران خیلی بزرگ‌تر است.</t>
+        </is>
+      </c>
+      <c r="F172" s="5" t="inlineStr">
+        <is>
+          <t>مرد</t>
+        </is>
+      </c>
+      <c r="G172" s="5" t="inlineStr">
+        <is>
+          <t>آماده</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B173" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C173" s="7" t="inlineStr">
+        <is>
+          <t>نفر اول</t>
+        </is>
+      </c>
+      <c r="D173" s="8" t="inlineStr">
+        <is>
+          <t>Is your brother older than you?</t>
+        </is>
+      </c>
+      <c r="E173" s="8" t="inlineStr">
+        <is>
+          <t>برادرت از تو مسن‌تر است؟</t>
+        </is>
+      </c>
+      <c r="F173" s="7" t="inlineStr">
+        <is>
+          <t>زن</t>
+        </is>
+      </c>
+      <c r="G173" s="7" t="inlineStr">
+        <is>
+          <t>آماده</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B174" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C174" s="5" t="inlineStr">
+        <is>
+          <t>نفر دوم</t>
+        </is>
+      </c>
+      <c r="D174" s="6" t="inlineStr">
+        <is>
+          <t>Yes, he's two years older.</t>
+        </is>
+      </c>
+      <c r="E174" s="6" t="inlineStr">
+        <is>
+          <t>بله، دو سال مسن‌تر است.</t>
+        </is>
+      </c>
+      <c r="F174" s="5" t="inlineStr">
+        <is>
+          <t>مرد</t>
+        </is>
+      </c>
+      <c r="G174" s="5" t="inlineStr">
+        <is>
+          <t>آماده</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B175" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C175" s="7" t="inlineStr">
+        <is>
+          <t>نفر اول</t>
+        </is>
+      </c>
+      <c r="D175" s="8" t="inlineStr">
+        <is>
+          <t>This tea is better than that one.</t>
+        </is>
+      </c>
+      <c r="E175" s="8" t="inlineStr">
+        <is>
+          <t>این چای از آن یکی بهتر است.</t>
+        </is>
+      </c>
+      <c r="F175" s="7" t="inlineStr">
+        <is>
+          <t>زن</t>
+        </is>
+      </c>
+      <c r="G175" s="7" t="inlineStr">
+        <is>
+          <t>آماده</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B176" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C176" s="5" t="inlineStr">
+        <is>
+          <t>نفر دوم</t>
+        </is>
+      </c>
+      <c r="D176" s="6" t="inlineStr">
+        <is>
+          <t>I agree. And it's cheaper too.</t>
+        </is>
+      </c>
+      <c r="E176" s="6" t="inlineStr">
+        <is>
+          <t>موافقم. و ارزان‌تر هم هست.</t>
+        </is>
+      </c>
+      <c r="F176" s="5" t="inlineStr">
+        <is>
+          <t>مرد</t>
+        </is>
+      </c>
+      <c r="G176" s="5" t="inlineStr">
+        <is>
+          <t>آماده</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="B169" s="7" t="n">
+      <c r="B177" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C177" s="7" t="inlineStr">
+        <is>
+          <t>نفر اول</t>
+        </is>
+      </c>
+      <c r="D177" s="8" t="inlineStr">
+        <is>
+          <t>How was your week?</t>
+        </is>
+      </c>
+      <c r="E177" s="8" t="inlineStr">
+        <is>
+          <t>هفته‌ات چطور بود؟</t>
+        </is>
+      </c>
+      <c r="F177" s="7" t="inlineStr">
+        <is>
+          <t>زن</t>
+        </is>
+      </c>
+      <c r="G177" s="7" t="inlineStr">
+        <is>
+          <t>آماده</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B178" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C178" s="5" t="inlineStr">
+        <is>
+          <t>نفر دوم</t>
+        </is>
+      </c>
+      <c r="D178" s="6" t="inlineStr">
+        <is>
+          <t>It was the best week of the year!</t>
+        </is>
+      </c>
+      <c r="E178" s="6" t="inlineStr">
+        <is>
+          <t>بهترین هفته سال بود!</t>
+        </is>
+      </c>
+      <c r="F178" s="5" t="inlineStr">
+        <is>
+          <t>مرد</t>
+        </is>
+      </c>
+      <c r="G178" s="5" t="inlineStr">
+        <is>
+          <t>آماده</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B179" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C179" s="7" t="inlineStr">
+        <is>
+          <t>نفر اول</t>
+        </is>
+      </c>
+      <c r="D179" s="8" t="inlineStr">
+        <is>
+          <t>Why? What happened?</t>
+        </is>
+      </c>
+      <c r="E179" s="8" t="inlineStr">
+        <is>
+          <t>چرا؟ چه شد؟</t>
+        </is>
+      </c>
+      <c r="F179" s="7" t="inlineStr">
+        <is>
+          <t>زن</t>
+        </is>
+      </c>
+      <c r="G179" s="7" t="inlineStr">
+        <is>
+          <t>آماده</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B180" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C180" s="5" t="inlineStr">
+        <is>
+          <t>نفر دوم</t>
+        </is>
+      </c>
+      <c r="D180" s="6" t="inlineStr">
+        <is>
+          <t>I finished level A1.</t>
+        </is>
+      </c>
+      <c r="E180" s="6" t="inlineStr">
+        <is>
+          <t>سطح A1 را تمام کردم.</t>
+        </is>
+      </c>
+      <c r="F180" s="5" t="inlineStr">
+        <is>
+          <t>مرد</t>
+        </is>
+      </c>
+      <c r="G180" s="5" t="inlineStr">
+        <is>
+          <t>آماده</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B181" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C181" s="7" t="inlineStr">
+        <is>
+          <t>نفر اول</t>
+        </is>
+      </c>
+      <c r="D181" s="8" t="inlineStr">
+        <is>
+          <t>Well done! I'm proud of you.</t>
+        </is>
+      </c>
+      <c r="E181" s="8" t="inlineStr">
+        <is>
+          <t>آفرین! به تو افتخار می‌کنم.</t>
+        </is>
+      </c>
+      <c r="F181" s="7" t="inlineStr">
+        <is>
+          <t>زن</t>
+        </is>
+      </c>
+      <c r="G181" s="7" t="inlineStr">
+        <is>
+          <t>آماده</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B182" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="C169" s="7" t="inlineStr">
+      <c r="C182" s="5" t="inlineStr">
         <is>
           <t>نفر دوم</t>
         </is>
       </c>
-      <c r="D169" s="8" t="inlineStr">
+      <c r="D182" s="6" t="inlineStr">
         <is>
           <t>Thank you. Now I'm ready for A2.</t>
         </is>
       </c>
-      <c r="E169" s="8" t="inlineStr">
+      <c r="E182" s="6" t="inlineStr">
         <is>
           <t>ممنون. حالا برای A2 آماده‌ام.</t>
         </is>
       </c>
-      <c r="F169" s="7" t="inlineStr">
+      <c r="F182" s="5" t="inlineStr">
         <is>
           <t>مرد</t>
         </is>
       </c>
-      <c r="G169" s="7" t="inlineStr">
+      <c r="G182" s="5" t="inlineStr">
         <is>
           <t>آماده</t>
         </is>

--- a/content/A1-محتوا.xlsx
+++ b/content/A1-محتوا.xlsx
@@ -497,12 +497,8 @@
           <t>کاربرگ محتوای سطح A1</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="2"/>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -47899,7 +47895,7 @@
       </c>
       <c r="J9" s="8" t="inlineStr">
         <is>
-          <t>عبارت را واضح تلفظ کنید.</t>
+          <t>عبارت را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
@@ -48287,7 +48283,7 @@
       </c>
       <c r="J17" s="8" t="inlineStr">
         <is>
-          <t>عبارت را واضح تلفظ کنید.</t>
+          <t>عبارت را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
@@ -48675,7 +48671,7 @@
       </c>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>عبارت را واضح تلفظ کنید.</t>
+          <t>عبارت را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr">
@@ -49055,7 +49051,7 @@
       </c>
       <c r="J33" s="8" t="inlineStr">
         <is>
-          <t>عبارت را واضح تلفظ کنید.</t>
+          <t>عبارت را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K33" s="7" t="inlineStr">
@@ -49443,7 +49439,7 @@
       </c>
       <c r="J41" s="8" t="inlineStr">
         <is>
-          <t>عبارت را واضح تلفظ کنید.</t>
+          <t>عبارت را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr">
@@ -49831,7 +49827,7 @@
       </c>
       <c r="J49" s="8" t="inlineStr">
         <is>
-          <t>عبارت را واضح تلفظ کنید.</t>
+          <t>عبارت را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr">
@@ -50227,7 +50223,7 @@
       </c>
       <c r="J57" s="8" t="inlineStr">
         <is>
-          <t>عبارت را واضح تلفظ کنید.</t>
+          <t>عبارت را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K57" s="7" t="inlineStr">
@@ -50615,7 +50611,7 @@
       </c>
       <c r="J65" s="8" t="inlineStr">
         <is>
-          <t>عبارت را واضح تلفظ کنید.</t>
+          <t>عبارت را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K65" s="7" t="inlineStr">
@@ -50999,7 +50995,7 @@
       </c>
       <c r="J73" s="8" t="inlineStr">
         <is>
-          <t>عبارت را واضح تلفظ کنید.</t>
+          <t>عبارت را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K73" s="7" t="inlineStr">
@@ -51391,7 +51387,7 @@
       </c>
       <c r="J81" s="8" t="inlineStr">
         <is>
-          <t>عبارت را واضح تلفظ کنید.</t>
+          <t>عبارت را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K81" s="7" t="inlineStr">
@@ -51779,7 +51775,7 @@
       </c>
       <c r="J89" s="8" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K89" s="7" t="inlineStr">
@@ -52171,7 +52167,7 @@
       </c>
       <c r="J97" s="8" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K97" s="7" t="inlineStr">
@@ -52563,7 +52559,7 @@
       </c>
       <c r="J105" s="8" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K105" s="7" t="inlineStr">
@@ -52959,7 +52955,7 @@
       </c>
       <c r="J113" s="8" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K113" s="7" t="inlineStr">
@@ -53347,7 +53343,7 @@
       </c>
       <c r="J121" s="8" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K121" s="7" t="inlineStr">
@@ -53739,7 +53735,7 @@
       </c>
       <c r="J129" s="8" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K129" s="7" t="inlineStr">
@@ -54123,7 +54119,7 @@
       </c>
       <c r="J137" s="8" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K137" s="7" t="inlineStr">
@@ -54519,7 +54515,7 @@
       </c>
       <c r="J145" s="8" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K145" s="7" t="inlineStr">
@@ -54911,7 +54907,7 @@
       </c>
       <c r="J153" s="8" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K153" s="7" t="inlineStr">
@@ -55303,7 +55299,7 @@
       </c>
       <c r="J161" s="8" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K161" s="7" t="inlineStr">
@@ -55695,7 +55691,7 @@
       </c>
       <c r="J169" s="8" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K169" s="7" t="inlineStr">
@@ -56091,7 +56087,7 @@
       </c>
       <c r="J177" s="8" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K177" s="7" t="inlineStr">
@@ -56475,7 +56471,7 @@
       </c>
       <c r="J185" s="8" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K185" s="7" t="inlineStr">
@@ -56863,7 +56859,7 @@
       </c>
       <c r="J193" s="8" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K193" s="7" t="inlineStr">
@@ -57251,7 +57247,7 @@
       </c>
       <c r="J201" s="8" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K201" s="7" t="inlineStr">
@@ -57639,7 +57635,7 @@
       </c>
       <c r="J209" s="8" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K209" s="7" t="inlineStr">
@@ -58023,7 +58019,7 @@
       </c>
       <c r="J217" s="8" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K217" s="7" t="inlineStr">
@@ -58415,7 +58411,7 @@
       </c>
       <c r="J225" s="8" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K225" s="7" t="inlineStr">
@@ -58803,7 +58799,7 @@
       </c>
       <c r="J233" s="8" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K233" s="7" t="inlineStr">
@@ -59199,7 +59195,7 @@
       </c>
       <c r="J241" s="8" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K241" s="7" t="inlineStr">
